--- a/Excel/PELMET.xlsx
+++ b/Excel/PELMET.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A6C8FD-7E8C-4D64-8968-4BDEC75F7E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32304AC-A762-422D-A0FE-07AF77B2062D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{4D0A880C-4B9B-4C7C-BD4D-01AC8F1A62F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{4D0A880C-4B9B-4C7C-BD4D-01AC8F1A62F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
   <si>
     <t>Order Number</t>
   </si>
@@ -112,6 +112,30 @@
   </si>
   <si>
     <t>RETURN LENGTH (R)</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Both Sides</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>PELMET</t>
   </si>
 </sst>
 </file>
@@ -463,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E020DE3-5F6C-4C72-8481-139FEAF97011}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -493,11 +517,11 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -578,6 +602,18 @@
       <c r="J4" t="s">
         <v>26</v>
       </c>
+      <c r="K4">
+        <v>1000</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -598,61 +634,96 @@
       <c r="F5" t="s">
         <v>25</v>
       </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="L5">
+        <v>1000</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
-      </c>
-      <c r="N6">
-        <v>14</v>
+        <v>1000</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
       </c>
       <c r="O6">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>16</v>
-      </c>
-      <c r="Q6">
-        <v>17</v>
-      </c>
-      <c r="R6">
-        <v>18</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1000</v>
+      </c>
+      <c r="M7">
+        <v>1000</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/PELMET.xlsx
+++ b/Excel/PELMET.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32304AC-A762-422D-A0FE-07AF77B2062D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CD66D8-A487-4A53-B2F7-2B466EBE7EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{4D0A880C-4B9B-4C7C-BD4D-01AC8F1A62F8}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Order Number</t>
   </si>
@@ -42,9 +42,6 @@
     <t>BLIND TYPE</t>
   </si>
   <si>
-    <t>TUBE TYPE</t>
-  </si>
-  <si>
     <t>QTY</t>
   </si>
   <si>
@@ -60,12 +57,6 @@
     <t>FABRIC COLOUR</t>
   </si>
   <si>
-    <t>TIMBER</t>
-  </si>
-  <si>
-    <t>PELMET LAYOUT</t>
-  </si>
-  <si>
     <t>WIDTH</t>
   </si>
   <si>
@@ -93,9 +84,6 @@
     <t>Pelmet 140mm</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Face Fit</t>
   </si>
   <si>
@@ -114,18 +102,6 @@
     <t>RETURN LENGTH (R)</t>
   </si>
   <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
-    <t>Both Sides</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -136,6 +112,15 @@
   </si>
   <si>
     <t>PELMET</t>
+  </si>
+  <si>
+    <t>PELMET TYPE</t>
+  </si>
+  <si>
+    <t>BATTEN COLOUR</t>
+  </si>
+  <si>
+    <t>LAYOUT</t>
   </si>
 </sst>
 </file>
@@ -151,12 +136,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -171,8 +162,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,12 +487,13 @@
     <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" customWidth="1"/>
     <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -518,212 +511,104 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L3" t="s">
+      <c r="O3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M3" t="s">
+      <c r="R3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>17</v>
-      </c>
-      <c r="R3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4">
-        <v>1000</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
       <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
         <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5">
-        <v>1000</v>
-      </c>
-      <c r="L5">
-        <v>1000</v>
-      </c>
-      <c r="N5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
       <c r="J6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6">
-        <v>1000</v>
-      </c>
-      <c r="L6">
-        <v>1000</v>
-      </c>
-      <c r="N6" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
-      <c r="P6">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
       <c r="J7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7">
-        <v>1000</v>
-      </c>
-      <c r="L7">
-        <v>1000</v>
-      </c>
-      <c r="M7">
-        <v>1000</v>
-      </c>
-      <c r="N7" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
